--- a/docs/100_鍵盤按鍵與編碼對映.xlsx
+++ b/docs/100_鍵盤按鍵與編碼對映.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E1747-256B-4009-9396-43D1F689CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611E3784-5E93-4B5D-A9BA-37430A5E83D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="700" activeTab="1" xr2:uid="{D79CAC63-F162-4D74-ACD7-2EADE37AC29E}"/>
+    <workbookView minimized="1" xWindow="4245" yWindow="5745" windowWidth="21600" windowHeight="11295" tabRatio="700" activeTab="4" xr2:uid="{D79CAC63-F162-4D74-ACD7-2EADE37AC29E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" activeTab="7" xr2:uid="{B739CF38-08F3-4214-89CB-36FDF4581D42}"/>
   </bookViews>
   <sheets>
     <sheet name="【聲】聲母對照表" sheetId="3" r:id="rId1"/>
@@ -286,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3084" uniqueCount="1248">
   <si>
     <t>huan_ciat_tps</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -25149,12 +25150,15 @@
         <v>4</v>
       </c>
       <c r="W1" s="24" t="s">
-        <v>3</v>
+        <v>743</v>
       </c>
       <c r="X1" s="24" t="s">
-        <v>6</v>
+        <v>1151</v>
       </c>
       <c r="Y1" s="24" t="s">
+        <v>742</v>
+      </c>
+      <c r="Z1" s="24" t="s">
         <v>571</v>
       </c>
       <c r="AC1" s="1" t="s">
@@ -25250,7 +25254,7 @@
         <v>1</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="V2" s="26">
         <v>1</v>
@@ -25258,8 +25262,11 @@
       <c r="W2" s="25">
         <v>1</v>
       </c>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6" t="s">
+      <c r="X2" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6" t="s">
         <v>605</v>
       </c>
       <c r="AE2" s="4" cm="1">
@@ -25602,8 +25609,8 @@
       <c r="T3" s="5">
         <v>2</v>
       </c>
-      <c r="U3" s="6" t="s">
-        <v>233</v>
+      <c r="U3" s="6">
+        <v>5</v>
       </c>
       <c r="V3" s="25">
         <v>7</v>
@@ -25612,9 +25619,12 @@
         <v>7</v>
       </c>
       <c r="X3" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="Y3" s="6" t="s">
         <v>726</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>611</v>
       </c>
       <c r="AC3" s="7" t="s">
@@ -25904,8 +25914,8 @@
       <c r="T4" s="5">
         <v>3</v>
       </c>
-      <c r="U4" s="6" t="s">
-        <v>617</v>
+      <c r="U4" s="6">
+        <v>3</v>
       </c>
       <c r="V4" s="25">
         <v>3</v>
@@ -25914,9 +25924,12 @@
         <v>3</v>
       </c>
       <c r="X4" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>727</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>619</v>
       </c>
       <c r="AC4" s="13" t="s">
@@ -26260,8 +26273,8 @@
       <c r="T5" s="5">
         <v>4</v>
       </c>
-      <c r="U5" s="6" t="s">
-        <v>623</v>
+      <c r="U5" s="6">
+        <v>4</v>
       </c>
       <c r="V5" s="25">
         <v>2</v>
@@ -26270,9 +26283,12 @@
         <v>2</v>
       </c>
       <c r="X5" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>725</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>624</v>
       </c>
       <c r="AC5" s="17" t="s">
@@ -26617,8 +26633,8 @@
       <c r="T6" s="5">
         <v>5</v>
       </c>
-      <c r="U6" s="6" t="s">
-        <v>121</v>
+      <c r="U6" s="6">
+        <v>6</v>
       </c>
       <c r="V6" s="25">
         <v>5</v>
@@ -26627,9 +26643,12 @@
         <v>5</v>
       </c>
       <c r="X6" s="6" t="s">
+        <v>1156</v>
+      </c>
+      <c r="Y6" s="6" t="s">
         <v>724</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>618</v>
       </c>
       <c r="AC6" s="21" t="s">
@@ -26982,8 +27001,11 @@
       <c r="W7" s="25">
         <v>4</v>
       </c>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6" t="s">
+      <c r="X7" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6" t="s">
         <v>631</v>
       </c>
       <c r="AE7" s="12"/>
@@ -27156,9 +27178,12 @@
         <v>8</v>
       </c>
       <c r="X8" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y8" s="6" t="s">
         <v>728</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>637</v>
       </c>
       <c r="AC8" s="1" t="s">
@@ -27321,9 +27346,27 @@
       <c r="R9" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="T9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
+      <c r="T9" s="5">
+        <v>8</v>
+      </c>
+      <c r="U9" s="6">
+        <v>7</v>
+      </c>
+      <c r="V9" s="25">
+        <v>0</v>
+      </c>
+      <c r="W9" s="25">
+        <v>0</v>
+      </c>
+      <c r="X9" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y9" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>1214</v>
+      </c>
       <c r="AC9" s="1" t="s">
         <v>189</v>
       </c>
@@ -27487,9 +27530,6 @@
       <c r="R10" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="T10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
       <c r="AC10" s="1" t="s">
         <v>191</v>
       </c>
@@ -27654,9 +27694,6 @@
       <c r="R11" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="T11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
       <c r="AC11" s="1" t="s">
         <v>193</v>
       </c>
@@ -27816,16 +27853,13 @@
         <v>4</v>
       </c>
       <c r="W12" s="24" t="s">
-        <v>729</v>
+        <v>3</v>
       </c>
       <c r="X12" s="24" t="s">
-        <v>730</v>
-      </c>
-      <c r="Y12" s="113" t="s">
-        <v>731</v>
-      </c>
-      <c r="Z12" s="66" t="s">
-        <v>737</v>
+        <v>6</v>
+      </c>
+      <c r="Y12" s="24" t="s">
+        <v>571</v>
       </c>
       <c r="AD12" s="137"/>
       <c r="AE12" s="137"/>
@@ -27933,14 +27967,9 @@
       <c r="W13" s="25">
         <v>1</v>
       </c>
-      <c r="X13" s="6" t="s">
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6" t="s">
         <v>605</v>
-      </c>
-      <c r="Y13" s="6" t="s">
-        <v>712</v>
-      </c>
-      <c r="Z13" s="6" t="s">
-        <v>373</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>199</v>
@@ -28039,16 +28068,13 @@
         <v>7</v>
       </c>
       <c r="W14" s="25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14" s="6" t="s">
-        <v>610</v>
+        <v>726</v>
       </c>
       <c r="Y14" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="Z14" s="6" t="s">
-        <v>734</v>
+        <v>611</v>
       </c>
       <c r="AE14" s="176" t="s">
         <v>1212</v>
@@ -28204,16 +28230,13 @@
         <v>3</v>
       </c>
       <c r="W15" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X15" s="6" t="s">
-        <v>618</v>
+        <v>727</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="Z15" s="6" t="s">
-        <v>370</v>
+        <v>619</v>
       </c>
       <c r="AE15" s="154" t="s">
         <v>1209</v>
@@ -28310,16 +28333,13 @@
         <v>2</v>
       </c>
       <c r="W16" s="25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>619</v>
+        <v>725</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="Z16" s="6" t="s">
-        <v>732</v>
+        <v>624</v>
       </c>
       <c r="AC16" s="1" t="s">
         <v>206</v>
@@ -28421,16 +28441,13 @@
         <v>5</v>
       </c>
       <c r="W17" s="25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X17" s="6" t="s">
-        <v>624</v>
+        <v>724</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>716</v>
-      </c>
-      <c r="Z17" s="6" t="s">
-        <v>369</v>
+        <v>618</v>
       </c>
       <c r="AC17" s="1" t="s">
         <v>209</v>
@@ -28532,16 +28549,11 @@
         <v>4</v>
       </c>
       <c r="W18" s="25">
-        <v>7</v>
-      </c>
-      <c r="X18" s="6" t="s">
-        <v>611</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="X18" s="6"/>
       <c r="Y18" s="6" t="s">
-        <v>733</v>
-      </c>
-      <c r="Z18" s="6" t="s">
-        <v>373</v>
+        <v>631</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>211</v>
@@ -28646,13 +28658,10 @@
         <v>8</v>
       </c>
       <c r="X19" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="Y19" s="6" t="s">
         <v>637</v>
-      </c>
-      <c r="Y19" s="6" t="s">
-        <v>736</v>
-      </c>
-      <c r="Z19" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="AD19" s="137"/>
       <c r="AE19" s="137"/>
@@ -28834,6 +28843,9 @@
       <c r="R21" s="6" t="s">
         <v>738</v>
       </c>
+      <c r="T21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
       <c r="AC21" s="1" t="s">
         <v>218</v>
       </c>
@@ -28927,6 +28939,9 @@
       <c r="R22" s="6" t="s">
         <v>422</v>
       </c>
+      <c r="T22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
       <c r="CN22" s="5">
         <v>21</v>
       </c>
@@ -29009,6 +29024,27 @@
       <c r="R23" s="6" t="s">
         <v>499</v>
       </c>
+      <c r="T23" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="U23" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="V23" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="W23" s="24" t="s">
+        <v>729</v>
+      </c>
+      <c r="X23" s="24" t="s">
+        <v>730</v>
+      </c>
+      <c r="Y23" s="113" t="s">
+        <v>731</v>
+      </c>
+      <c r="Z23" s="66" t="s">
+        <v>737</v>
+      </c>
       <c r="AE23" s="4" cm="1">
         <f t="array" ref="AE23" xml:space="preserve"> COLUMN() - COLUMN($AD:$AD)</f>
         <v>1</v>
@@ -29291,6 +29327,27 @@
       <c r="R24" s="6" t="s">
         <v>388</v>
       </c>
+      <c r="T24" s="5">
+        <v>1</v>
+      </c>
+      <c r="U24" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="V24" s="26">
+        <v>1</v>
+      </c>
+      <c r="W24" s="25">
+        <v>1</v>
+      </c>
+      <c r="X24" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="Y24" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="Z24" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="AC24" s="13" t="s">
         <v>66</v>
       </c>
@@ -29576,6 +29633,27 @@
       <c r="R25" s="6" t="s">
         <v>739</v>
       </c>
+      <c r="T25" s="5">
+        <v>2</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="V25" s="25">
+        <v>7</v>
+      </c>
+      <c r="W25" s="25">
+        <v>6</v>
+      </c>
+      <c r="X25" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="Y25" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="Z25" s="6" t="s">
+        <v>734</v>
+      </c>
       <c r="AC25" s="17" t="s">
         <v>110</v>
       </c>
@@ -29860,6 +29938,27 @@
       <c r="R26" s="6" t="s">
         <v>61</v>
       </c>
+      <c r="T26" s="5">
+        <v>3</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="V26" s="25">
+        <v>3</v>
+      </c>
+      <c r="W26" s="25">
+        <v>5</v>
+      </c>
+      <c r="X26" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="Y26" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="Z26" s="6" t="s">
+        <v>370</v>
+      </c>
       <c r="CT26" s="5">
         <v>25</v>
       </c>
@@ -29901,6 +30000,27 @@
       <c r="R27" s="6" t="s">
         <v>140</v>
       </c>
+      <c r="T27" s="5">
+        <v>4</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="V27" s="25">
+        <v>2</v>
+      </c>
+      <c r="W27" s="25">
+        <v>3</v>
+      </c>
+      <c r="X27" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="Y27" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="Z27" s="6" t="s">
+        <v>732</v>
+      </c>
       <c r="CT27" s="5">
         <v>26</v>
       </c>
@@ -29942,6 +30062,27 @@
       <c r="R28" s="6" t="s">
         <v>144</v>
       </c>
+      <c r="T28" s="5">
+        <v>5</v>
+      </c>
+      <c r="U28" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="V28" s="25">
+        <v>5</v>
+      </c>
+      <c r="W28" s="25">
+        <v>2</v>
+      </c>
+      <c r="X28" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="Y28" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="Z28" s="6" t="s">
+        <v>369</v>
+      </c>
       <c r="AC28" s="1" t="s">
         <v>229</v>
       </c>
@@ -29985,6 +30126,27 @@
       </c>
       <c r="R29" s="6" t="s">
         <v>151</v>
+      </c>
+      <c r="T29" s="5">
+        <v>6</v>
+      </c>
+      <c r="U29" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="V29" s="25">
+        <v>4</v>
+      </c>
+      <c r="W29" s="25">
+        <v>7</v>
+      </c>
+      <c r="X29" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="Y29" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="Z29" s="6" t="s">
+        <v>373</v>
       </c>
       <c r="AE29" s="176" t="s">
         <v>1213</v>
@@ -30072,6 +30234,27 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
+      <c r="T30" s="5">
+        <v>7</v>
+      </c>
+      <c r="U30" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="V30" s="25">
+        <v>8</v>
+      </c>
+      <c r="W30" s="25">
+        <v>8</v>
+      </c>
+      <c r="X30" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="Y30" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="Z30" s="6" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="31" spans="2:102" outlineLevel="1">
       <c r="L31" s="1"/>
@@ -30081,6 +30264,9 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
+      <c r="T31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
       <c r="AC31" s="1" t="s">
         <v>206</v>
       </c>
@@ -38758,11 +38944,10 @@
       <c r="U16" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="Z16" s="158" t="str">
+      <c r="AA16" s="158" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", AA14, "|", AA15, "|")</f>
         <v xml:space="preserve">    - xlit|BbpmdtnlĞgkŋhZzcsJjCSaiwueOəIUDfqrvxyMGNY@AWHRFQVØL&amp;17325480|!1qa2wsxEedNcYyhnRrfv8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz=-."5346[]7|</v>
       </c>
-      <c r="AA16" s="159"/>
       <c r="AB16" s="159"/>
       <c r="AC16" s="159"/>
       <c r="AD16" s="159"/>
@@ -38996,7 +39181,7 @@
         <v>206</v>
       </c>
       <c r="Z18" s="137">
-        <f xml:space="preserve"> SEARCH("|", $Z$16)</f>
+        <f xml:space="preserve"> SEARCH("|", $AA$16)</f>
         <v>11</v>
       </c>
       <c r="CJ18" s="5">
@@ -39089,7 +39274,7 @@
         <v>209</v>
       </c>
       <c r="Z19" s="137">
-        <f xml:space="preserve"> SEARCH("|", $Z$16, Z18+1)</f>
+        <f xml:space="preserve"> SEARCH("|", $AA$16, Z18+1)</f>
         <v>72</v>
       </c>
       <c r="CJ19" s="5">
@@ -39167,7 +39352,7 @@
         <v>211</v>
       </c>
       <c r="Z20" s="137">
-        <f xml:space="preserve"> SEARCH("|", $Z$16, Z19+1)</f>
+        <f xml:space="preserve"> SEARCH("|", $AA$16, Z19+1)</f>
         <v>133</v>
       </c>
       <c r="CJ20" s="5">
@@ -39320,7 +39505,7 @@
         <v>60</v>
       </c>
       <c r="AA22" s="137" t="str">
-        <f xml:space="preserve"> MID($Z$16, Z18+1, (Z19-Z18-1))</f>
+        <f xml:space="preserve"> MID($AA$16, Z18+1, (Z19-Z18-1))</f>
         <v>BbpmdtnlĞgkŋhZzcsJjCSaiwueOəIUDfqrvxyMGNY@AWHRFQVØL&amp;17325480</v>
       </c>
       <c r="CJ22" s="5">
@@ -39420,7 +39605,7 @@
         <v>60</v>
       </c>
       <c r="AA23" s="137" t="str">
-        <f xml:space="preserve"> MID($Z$16, Z19+1, (Z20-Z19-1))</f>
+        <f xml:space="preserve"> MID($AA$16, Z19+1, (Z20-Z19-1))</f>
         <v>!1qa2wsxEedNcYyhnRrfv8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz=-."5346[]7</v>
       </c>
       <c r="CP23" s="5">
@@ -40729,11 +40914,10 @@
         <v>181</v>
       </c>
       <c r="Y33" s="153"/>
-      <c r="Z33" s="158" t="str">
+      <c r="AA33" s="158" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", AA31, "|", AA32, "|")</f>
         <v xml:space="preserve">    - xlit|!1qa2wsxEedNcYyhnRrfv8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz=-."5346[]7|ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㄏㆡㄗㄘㄙㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷØㄥ入一七三二五四八ʔ|</v>
       </c>
-      <c r="AA33" s="159"/>
       <c r="AB33" s="159"/>
       <c r="AC33" s="159"/>
       <c r="AD33" s="159"/>
@@ -40991,7 +41175,7 @@
         <v>206</v>
       </c>
       <c r="Z36" s="137">
-        <f xml:space="preserve"> SEARCH("|", $Z$33)</f>
+        <f xml:space="preserve"> SEARCH("|", $AA$33)</f>
         <v>11</v>
       </c>
     </row>
@@ -41005,7 +41189,7 @@
         <v>209</v>
       </c>
       <c r="Z37" s="137">
-        <f xml:space="preserve"> SEARCH("|", $Z$33, Z36+1)</f>
+        <f xml:space="preserve"> SEARCH("|", $AA$33, Z36+1)</f>
         <v>72</v>
       </c>
     </row>
@@ -41019,7 +41203,7 @@
         <v>211</v>
       </c>
       <c r="Z38" s="137">
-        <f xml:space="preserve"> SEARCH("|", $Z$33, Z37+1)</f>
+        <f xml:space="preserve"> SEARCH("|", $AA$33, Z37+1)</f>
         <v>133</v>
       </c>
     </row>
@@ -41044,7 +41228,7 @@
         <v>60</v>
       </c>
       <c r="AA40" s="137" t="str">
-        <f xml:space="preserve"> MID($Z$33, Z36+1, (Z37-Z36-1))</f>
+        <f xml:space="preserve"> MID($AA$33, Z36+1, (Z37-Z36-1))</f>
         <v>!1qa2wsxEedNcYyhnRrfv8uKj,ik9l*UJ&lt;I(Lm/pM0;Oobtgz=-."5346[]7</v>
       </c>
     </row>
@@ -41062,7 +41246,7 @@
         <v>60</v>
       </c>
       <c r="AA41" s="137" t="str">
-        <f xml:space="preserve"> MID($Z$33, Z37+1, (Z38-Z37-1))</f>
+        <f xml:space="preserve"> MID($AA$33, Z37+1, (Z38-Z37-1))</f>
         <v>ㆠㄅㄆㄇㄉㄊㄋㄌㆣㄍㄎㄫㄏㆡㄗㄘㄙㆢㄐㄑㄒㄚㄧㆨㄨㆤㆦㄜㄞㄠㆩㆪㆫㆥㆧㆮㆯㆬㆭㄣㆰㄢㄤㆱㆲㆴㆵㆻㆷØㄥ入一七三二五四八ʔ</v>
       </c>
     </row>

--- a/docs/100_鍵盤按鍵與編碼對映.xlsx
+++ b/docs/100_鍵盤按鍵與編碼對映.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803E9E5C-6CA7-4F7E-9C00-A215FD451E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40932250-311B-47D1-93E7-3A81F02E023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="708" activeTab="1" xr2:uid="{B739CF38-08F3-4214-89CB-36FDF4581D42}"/>
+    <workbookView xWindow="-4800" yWindow="360" windowWidth="38640" windowHeight="15720" tabRatio="708" xr2:uid="{B739CF38-08F3-4214-89CB-36FDF4581D42}"/>
   </bookViews>
   <sheets>
     <sheet name="【拼音類】鍵盤" sheetId="14" r:id="rId1"/>
@@ -11803,39 +11803,6 @@
     <xf numFmtId="0" fontId="68" fillId="23" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="24" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="24" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="24" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="24" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="24" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="24" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="162" fillId="18" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -11893,24 +11860,6 @@
     <xf numFmtId="0" fontId="165" fillId="24" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="166" fillId="24" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="24" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="24" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="24" borderId="25" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="24" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="24" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="165" fillId="18" borderId="22" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -11931,6 +11880,57 @@
     </xf>
     <xf numFmtId="9" fontId="162" fillId="19" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="24" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="24" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="24" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="24" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="24" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="24" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="24" borderId="25" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="24" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="24" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="24" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="24" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="24" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -13911,66 +13911,66 @@
     </row>
     <row r="2" spans="1:45" s="197" customFormat="1" ht="60" customHeight="1">
       <c r="A2" s="198"/>
-      <c r="B2" s="360" t="s">
+      <c r="B2" s="349" t="s">
         <v>1247</v>
       </c>
-      <c r="C2" s="355"/>
-      <c r="D2" s="356"/>
-      <c r="E2" s="360" t="s">
+      <c r="C2" s="344"/>
+      <c r="D2" s="345"/>
+      <c r="E2" s="349" t="s">
         <v>1248</v>
       </c>
-      <c r="F2" s="355"/>
-      <c r="G2" s="356"/>
-      <c r="H2" s="360" t="s">
+      <c r="F2" s="344"/>
+      <c r="G2" s="345"/>
+      <c r="H2" s="349" t="s">
         <v>1249</v>
       </c>
-      <c r="I2" s="355"/>
-      <c r="J2" s="356"/>
-      <c r="K2" s="360" t="s">
+      <c r="I2" s="344"/>
+      <c r="J2" s="345"/>
+      <c r="K2" s="349" t="s">
         <v>1250</v>
       </c>
-      <c r="L2" s="355"/>
-      <c r="M2" s="356"/>
-      <c r="N2" s="370" t="s">
+      <c r="L2" s="344"/>
+      <c r="M2" s="345"/>
+      <c r="N2" s="353" t="s">
         <v>1333</v>
       </c>
-      <c r="O2" s="355"/>
-      <c r="P2" s="356"/>
-      <c r="Q2" s="360" t="s">
+      <c r="O2" s="344"/>
+      <c r="P2" s="345"/>
+      <c r="Q2" s="349" t="s">
         <v>1251</v>
       </c>
-      <c r="R2" s="355"/>
-      <c r="S2" s="356"/>
-      <c r="T2" s="361" t="s">
+      <c r="R2" s="344"/>
+      <c r="S2" s="345"/>
+      <c r="T2" s="350" t="s">
         <v>1252</v>
       </c>
-      <c r="U2" s="362"/>
-      <c r="V2" s="363"/>
-      <c r="W2" s="357" t="s">
+      <c r="U2" s="351"/>
+      <c r="V2" s="352"/>
+      <c r="W2" s="346" t="s">
         <v>1253</v>
       </c>
-      <c r="X2" s="358"/>
-      <c r="Y2" s="359"/>
-      <c r="Z2" s="357" t="s">
+      <c r="X2" s="347"/>
+      <c r="Y2" s="348"/>
+      <c r="Z2" s="346" t="s">
         <v>1254</v>
       </c>
-      <c r="AA2" s="358"/>
-      <c r="AB2" s="359"/>
-      <c r="AC2" s="357" t="s">
+      <c r="AA2" s="347"/>
+      <c r="AB2" s="348"/>
+      <c r="AC2" s="346" t="s">
         <v>1255</v>
       </c>
-      <c r="AD2" s="358"/>
-      <c r="AE2" s="359"/>
-      <c r="AF2" s="361" t="s">
+      <c r="AD2" s="347"/>
+      <c r="AE2" s="348"/>
+      <c r="AF2" s="350" t="s">
         <v>1256</v>
       </c>
-      <c r="AG2" s="362"/>
-      <c r="AH2" s="363"/>
-      <c r="AI2" s="357" t="s">
+      <c r="AG2" s="351"/>
+      <c r="AH2" s="352"/>
+      <c r="AI2" s="346" t="s">
         <v>1257</v>
       </c>
-      <c r="AJ2" s="358"/>
-      <c r="AK2" s="359"/>
+      <c r="AJ2" s="347"/>
+      <c r="AK2" s="348"/>
       <c r="AL2" s="198"/>
       <c r="AM2" s="198"/>
       <c r="AN2" s="198"/>
@@ -14000,11 +14000,11 @@
       <c r="Q3" s="282"/>
       <c r="R3" s="217"/>
       <c r="S3" s="283"/>
-      <c r="T3" s="367" t="s">
+      <c r="T3" s="366" t="s">
         <v>1332</v>
       </c>
-      <c r="U3" s="368"/>
-      <c r="V3" s="369"/>
+      <c r="U3" s="367"/>
+      <c r="V3" s="368"/>
       <c r="W3" s="227"/>
       <c r="X3" s="228"/>
       <c r="Y3" s="229"/>
@@ -14014,11 +14014,11 @@
       <c r="AC3" s="231"/>
       <c r="AD3" s="228"/>
       <c r="AE3" s="232"/>
-      <c r="AF3" s="339" t="s">
+      <c r="AF3" s="363" t="s">
         <v>1326</v>
       </c>
-      <c r="AG3" s="340"/>
-      <c r="AH3" s="341"/>
+      <c r="AG3" s="364"/>
+      <c r="AH3" s="365"/>
       <c r="AI3" s="233"/>
       <c r="AJ3" s="234"/>
       <c r="AK3" s="235"/>
@@ -14051,11 +14051,11 @@
       <c r="Q4" s="289"/>
       <c r="R4" s="242"/>
       <c r="S4" s="291"/>
-      <c r="T4" s="342" t="s">
+      <c r="T4" s="369" t="s">
         <v>1331</v>
       </c>
-      <c r="U4" s="343"/>
-      <c r="V4" s="344" t="s">
+      <c r="U4" s="370"/>
+      <c r="V4" s="371" t="s">
         <v>1265</v>
       </c>
       <c r="W4" s="250"/>
@@ -14067,11 +14067,11 @@
       <c r="AC4" s="253"/>
       <c r="AD4" s="251"/>
       <c r="AE4" s="252"/>
-      <c r="AF4" s="364" t="s">
+      <c r="AF4" s="360" t="s">
         <v>1334</v>
       </c>
-      <c r="AG4" s="365"/>
-      <c r="AH4" s="366" t="s">
+      <c r="AG4" s="361"/>
+      <c r="AH4" s="362" t="s">
         <v>1268</v>
       </c>
       <c r="AI4" s="257"/>
@@ -14089,71 +14089,71 @@
     <row r="5" spans="1:45" s="197" customFormat="1" ht="60" customHeight="1">
       <c r="A5" s="198"/>
       <c r="B5" s="198"/>
-      <c r="C5" s="360" t="s">
+      <c r="C5" s="349" t="s">
         <v>201</v>
       </c>
-      <c r="D5" s="355"/>
-      <c r="E5" s="356"/>
-      <c r="F5" s="360" t="s">
+      <c r="D5" s="344"/>
+      <c r="E5" s="345"/>
+      <c r="F5" s="349" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="355"/>
-      <c r="H5" s="356"/>
-      <c r="I5" s="360" t="s">
+      <c r="G5" s="344"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="349" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="355"/>
-      <c r="K5" s="356"/>
-      <c r="L5" s="360" t="s">
+      <c r="J5" s="344"/>
+      <c r="K5" s="345"/>
+      <c r="L5" s="349" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="355"/>
-      <c r="N5" s="356"/>
-      <c r="O5" s="360" t="s">
+      <c r="M5" s="344"/>
+      <c r="N5" s="345"/>
+      <c r="O5" s="349" t="s">
         <v>71</v>
       </c>
-      <c r="P5" s="355"/>
-      <c r="Q5" s="356"/>
-      <c r="R5" s="360" t="s">
+      <c r="P5" s="344"/>
+      <c r="Q5" s="345"/>
+      <c r="R5" s="349" t="s">
         <v>114</v>
       </c>
-      <c r="S5" s="355"/>
-      <c r="T5" s="356"/>
-      <c r="U5" s="357" t="s">
+      <c r="S5" s="344"/>
+      <c r="T5" s="345"/>
+      <c r="U5" s="346" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="358"/>
-      <c r="W5" s="359"/>
-      <c r="X5" s="357" t="s">
+      <c r="V5" s="347"/>
+      <c r="W5" s="348"/>
+      <c r="X5" s="346" t="s">
         <v>94</v>
       </c>
-      <c r="Y5" s="358"/>
-      <c r="Z5" s="359"/>
-      <c r="AA5" s="357" t="s">
+      <c r="Y5" s="347"/>
+      <c r="Z5" s="348"/>
+      <c r="AA5" s="346" t="s">
         <v>86</v>
       </c>
-      <c r="AB5" s="358"/>
-      <c r="AC5" s="359"/>
-      <c r="AD5" s="357" t="s">
+      <c r="AB5" s="347"/>
+      <c r="AC5" s="348"/>
+      <c r="AD5" s="346" t="s">
         <v>67</v>
       </c>
-      <c r="AE5" s="358"/>
-      <c r="AF5" s="359"/>
-      <c r="AG5" s="361" t="s">
+      <c r="AE5" s="347"/>
+      <c r="AF5" s="348"/>
+      <c r="AG5" s="350" t="s">
         <v>1270</v>
       </c>
-      <c r="AH5" s="362"/>
-      <c r="AI5" s="363"/>
-      <c r="AJ5" s="361" t="s">
+      <c r="AH5" s="351"/>
+      <c r="AI5" s="352"/>
+      <c r="AJ5" s="350" t="s">
         <v>1271</v>
       </c>
-      <c r="AK5" s="362"/>
-      <c r="AL5" s="363"/>
-      <c r="AM5" s="361" t="s">
+      <c r="AK5" s="351"/>
+      <c r="AL5" s="352"/>
+      <c r="AM5" s="350" t="s">
         <v>1272</v>
       </c>
-      <c r="AN5" s="362"/>
-      <c r="AO5" s="363"/>
+      <c r="AN5" s="351"/>
+      <c r="AO5" s="352"/>
       <c r="AP5" s="198"/>
       <c r="AQ5" s="198"/>
       <c r="AR5" s="214"/>
@@ -14192,21 +14192,21 @@
       <c r="AD6" s="231"/>
       <c r="AE6" s="228"/>
       <c r="AF6" s="232"/>
-      <c r="AG6" s="339" t="s">
+      <c r="AG6" s="363" t="s">
         <v>1327</v>
       </c>
-      <c r="AH6" s="340"/>
-      <c r="AI6" s="341"/>
-      <c r="AJ6" s="339" t="s">
+      <c r="AH6" s="364"/>
+      <c r="AI6" s="365"/>
+      <c r="AJ6" s="363" t="s">
         <v>1328</v>
       </c>
-      <c r="AK6" s="340"/>
-      <c r="AL6" s="341"/>
-      <c r="AM6" s="339" t="s">
+      <c r="AK6" s="364"/>
+      <c r="AL6" s="365"/>
+      <c r="AM6" s="363" t="s">
         <v>1330</v>
       </c>
-      <c r="AN6" s="340"/>
-      <c r="AO6" s="341"/>
+      <c r="AN6" s="364"/>
+      <c r="AO6" s="365"/>
       <c r="AP6" s="198"/>
       <c r="AQ6" s="198"/>
       <c r="AR6" s="214"/>
@@ -14245,21 +14245,21 @@
       <c r="AD7" s="253"/>
       <c r="AE7" s="254"/>
       <c r="AF7" s="292"/>
-      <c r="AG7" s="364" t="s">
+      <c r="AG7" s="360" t="s">
         <v>1275</v>
       </c>
-      <c r="AH7" s="365"/>
-      <c r="AI7" s="366"/>
-      <c r="AJ7" s="364" t="s">
+      <c r="AH7" s="361"/>
+      <c r="AI7" s="362"/>
+      <c r="AJ7" s="360" t="s">
         <v>1277</v>
       </c>
-      <c r="AK7" s="365"/>
-      <c r="AL7" s="366"/>
-      <c r="AM7" s="364" t="s">
+      <c r="AK7" s="361"/>
+      <c r="AL7" s="362"/>
+      <c r="AM7" s="360" t="s">
         <v>1335</v>
       </c>
-      <c r="AN7" s="365"/>
-      <c r="AO7" s="366"/>
+      <c r="AN7" s="361"/>
+      <c r="AO7" s="362"/>
       <c r="AP7" s="240"/>
       <c r="AQ7" s="240"/>
       <c r="AR7" s="187"/>
@@ -14269,61 +14269,61 @@
       <c r="A8" s="198"/>
       <c r="B8" s="198"/>
       <c r="C8" s="294"/>
-      <c r="D8" s="360" t="s">
+      <c r="D8" s="349" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="355"/>
-      <c r="F8" s="356"/>
-      <c r="G8" s="360" t="s">
+      <c r="E8" s="344"/>
+      <c r="F8" s="345"/>
+      <c r="G8" s="349" t="s">
         <v>83</v>
       </c>
-      <c r="H8" s="355"/>
-      <c r="I8" s="356"/>
-      <c r="J8" s="360" t="s">
+      <c r="H8" s="344"/>
+      <c r="I8" s="345"/>
+      <c r="J8" s="349" t="s">
         <v>749</v>
       </c>
-      <c r="K8" s="355"/>
-      <c r="L8" s="356"/>
-      <c r="M8" s="360" t="s">
+      <c r="K8" s="344"/>
+      <c r="L8" s="345"/>
+      <c r="M8" s="349" t="s">
         <v>92</v>
       </c>
-      <c r="N8" s="355"/>
-      <c r="O8" s="356"/>
-      <c r="P8" s="360" t="s">
+      <c r="N8" s="344"/>
+      <c r="O8" s="345"/>
+      <c r="P8" s="349" t="s">
         <v>90</v>
       </c>
-      <c r="Q8" s="355"/>
-      <c r="R8" s="356"/>
-      <c r="S8" s="360" t="s">
+      <c r="Q8" s="344"/>
+      <c r="R8" s="345"/>
+      <c r="S8" s="349" t="s">
         <v>221</v>
       </c>
-      <c r="T8" s="355"/>
-      <c r="U8" s="356"/>
-      <c r="V8" s="357" t="s">
+      <c r="T8" s="344"/>
+      <c r="U8" s="345"/>
+      <c r="V8" s="346" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="358"/>
-      <c r="X8" s="359"/>
-      <c r="Y8" s="357" t="s">
+      <c r="W8" s="347"/>
+      <c r="X8" s="348"/>
+      <c r="Y8" s="346" t="s">
         <v>74</v>
       </c>
-      <c r="Z8" s="358"/>
-      <c r="AA8" s="359"/>
-      <c r="AB8" s="357" t="s">
+      <c r="Z8" s="347"/>
+      <c r="AA8" s="348"/>
+      <c r="AB8" s="346" t="s">
         <v>102</v>
       </c>
-      <c r="AC8" s="358"/>
-      <c r="AD8" s="359"/>
-      <c r="AE8" s="357" t="s">
+      <c r="AC8" s="347"/>
+      <c r="AD8" s="348"/>
+      <c r="AE8" s="350" t="s">
         <v>1278</v>
       </c>
-      <c r="AF8" s="358"/>
-      <c r="AG8" s="359"/>
-      <c r="AH8" s="361" t="s">
+      <c r="AF8" s="351"/>
+      <c r="AG8" s="352"/>
+      <c r="AH8" s="346" t="s">
         <v>1279</v>
       </c>
-      <c r="AI8" s="362"/>
-      <c r="AJ8" s="363"/>
+      <c r="AI8" s="347"/>
+      <c r="AJ8" s="348"/>
       <c r="AK8" s="198"/>
       <c r="AL8" s="198"/>
       <c r="AM8" s="198"/>
@@ -14365,14 +14365,14 @@
       <c r="AB9" s="227"/>
       <c r="AC9" s="228"/>
       <c r="AD9" s="229"/>
-      <c r="AE9" s="227"/>
-      <c r="AF9" s="228"/>
-      <c r="AG9" s="229"/>
-      <c r="AH9" s="339" t="s">
+      <c r="AE9" s="363" t="s">
         <v>1325</v>
       </c>
-      <c r="AI9" s="340"/>
-      <c r="AJ9" s="341"/>
+      <c r="AF9" s="364"/>
+      <c r="AG9" s="365"/>
+      <c r="AH9" s="227"/>
+      <c r="AI9" s="228"/>
+      <c r="AJ9" s="229"/>
       <c r="AK9" s="198"/>
       <c r="AL9" s="198"/>
       <c r="AM9" s="198"/>
@@ -14414,14 +14414,14 @@
       <c r="AB10" s="253"/>
       <c r="AC10" s="251"/>
       <c r="AD10" s="255"/>
-      <c r="AE10" s="253"/>
-      <c r="AF10" s="254"/>
-      <c r="AG10" s="255"/>
-      <c r="AH10" s="364" t="s">
+      <c r="AE10" s="360" t="s">
         <v>1324</v>
       </c>
-      <c r="AI10" s="365"/>
-      <c r="AJ10" s="366"/>
+      <c r="AF10" s="361"/>
+      <c r="AG10" s="362"/>
+      <c r="AH10" s="253"/>
+      <c r="AI10" s="251"/>
+      <c r="AJ10" s="255"/>
       <c r="AK10" s="240"/>
       <c r="AL10" s="240"/>
       <c r="AM10" s="240"/>
@@ -14437,56 +14437,56 @@
       <c r="B11" s="198"/>
       <c r="C11" s="198"/>
       <c r="D11" s="198"/>
-      <c r="E11" s="354" t="s">
+      <c r="E11" s="343" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="355"/>
-      <c r="G11" s="356"/>
-      <c r="H11" s="354" t="s">
+      <c r="F11" s="344"/>
+      <c r="G11" s="345"/>
+      <c r="H11" s="343" t="s">
         <v>1286</v>
       </c>
-      <c r="I11" s="355"/>
-      <c r="J11" s="356"/>
-      <c r="K11" s="354" t="s">
+      <c r="I11" s="344"/>
+      <c r="J11" s="345"/>
+      <c r="K11" s="343" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="355"/>
-      <c r="M11" s="356"/>
-      <c r="N11" s="354" t="s">
+      <c r="L11" s="344"/>
+      <c r="M11" s="345"/>
+      <c r="N11" s="343" t="s">
         <v>93</v>
       </c>
-      <c r="O11" s="355"/>
-      <c r="P11" s="356"/>
-      <c r="Q11" s="354" t="s">
+      <c r="O11" s="344"/>
+      <c r="P11" s="345"/>
+      <c r="Q11" s="343" t="s">
         <v>738</v>
       </c>
-      <c r="R11" s="355"/>
-      <c r="S11" s="356"/>
-      <c r="T11" s="354" t="s">
+      <c r="R11" s="344"/>
+      <c r="S11" s="345"/>
+      <c r="T11" s="343" t="s">
         <v>89</v>
       </c>
-      <c r="U11" s="355"/>
-      <c r="V11" s="356"/>
-      <c r="W11" s="357" t="s">
+      <c r="U11" s="344"/>
+      <c r="V11" s="345"/>
+      <c r="W11" s="346" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="358"/>
-      <c r="Y11" s="359"/>
-      <c r="Z11" s="357" t="s">
+      <c r="X11" s="347"/>
+      <c r="Y11" s="348"/>
+      <c r="Z11" s="346" t="s">
         <v>1287</v>
       </c>
-      <c r="AA11" s="358"/>
-      <c r="AB11" s="359"/>
-      <c r="AC11" s="361" t="s">
+      <c r="AA11" s="347"/>
+      <c r="AB11" s="348"/>
+      <c r="AC11" s="350" t="s">
         <v>1288</v>
       </c>
-      <c r="AD11" s="362"/>
-      <c r="AE11" s="363"/>
-      <c r="AF11" s="361" t="s">
+      <c r="AD11" s="351"/>
+      <c r="AE11" s="352"/>
+      <c r="AF11" s="350" t="s">
         <v>1289</v>
       </c>
-      <c r="AG11" s="362"/>
-      <c r="AH11" s="363"/>
+      <c r="AG11" s="351"/>
+      <c r="AH11" s="352"/>
       <c r="AI11" s="198"/>
       <c r="AJ11" s="198"/>
       <c r="AK11" s="198"/>
@@ -14528,14 +14528,14 @@
       <c r="Z12" s="227"/>
       <c r="AA12" s="230"/>
       <c r="AB12" s="229"/>
-      <c r="AC12" s="339"/>
-      <c r="AD12" s="340"/>
-      <c r="AE12" s="341"/>
-      <c r="AF12" s="339" t="s">
+      <c r="AC12" s="363"/>
+      <c r="AD12" s="364"/>
+      <c r="AE12" s="365"/>
+      <c r="AF12" s="363" t="s">
         <v>1329</v>
       </c>
-      <c r="AG12" s="340"/>
-      <c r="AH12" s="341"/>
+      <c r="AG12" s="364"/>
+      <c r="AH12" s="365"/>
       <c r="AI12" s="198"/>
       <c r="AJ12" s="198"/>
       <c r="AK12" s="198"/>
@@ -14579,14 +14579,14 @@
       <c r="Z13" s="253"/>
       <c r="AA13" s="251"/>
       <c r="AB13" s="255"/>
-      <c r="AC13" s="364"/>
-      <c r="AD13" s="365"/>
-      <c r="AE13" s="366"/>
-      <c r="AF13" s="364" t="s">
+      <c r="AC13" s="360"/>
+      <c r="AD13" s="361"/>
+      <c r="AE13" s="362"/>
+      <c r="AF13" s="360" t="s">
         <v>1324</v>
       </c>
-      <c r="AG13" s="365"/>
-      <c r="AH13" s="366"/>
+      <c r="AG13" s="361"/>
+      <c r="AH13" s="362"/>
       <c r="AI13" s="240"/>
       <c r="AJ13" s="240"/>
       <c r="AK13" s="240"/>
@@ -18443,6 +18443,8 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="AE9:AG9"/>
+    <mergeCell ref="AE10:AG10"/>
     <mergeCell ref="AC13:AE13"/>
     <mergeCell ref="AF13:AH13"/>
     <mergeCell ref="AM6:AO6"/>
@@ -18453,8 +18455,6 @@
     <mergeCell ref="AF4:AH4"/>
     <mergeCell ref="AC12:AE12"/>
     <mergeCell ref="AF12:AH12"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="AH9:AJ9"/>
     <mergeCell ref="AG6:AI6"/>
     <mergeCell ref="AJ6:AL6"/>
     <mergeCell ref="AG7:AI7"/>
@@ -18480,30 +18480,30 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:30" ht="30">
-      <c r="B3" s="334" t="s">
+      <c r="B3" s="372" t="s">
         <v>1201</v>
       </c>
-      <c r="C3" s="335"/>
-      <c r="D3" s="335"/>
-      <c r="E3" s="335"/>
-      <c r="F3" s="335"/>
-      <c r="G3" s="335"/>
-      <c r="H3" s="335"/>
-      <c r="I3" s="335"/>
-      <c r="J3" s="335"/>
-      <c r="K3" s="335"/>
-      <c r="L3" s="335"/>
-      <c r="M3" s="335"/>
-      <c r="N3" s="335"/>
-      <c r="O3" s="335"/>
-      <c r="P3" s="335"/>
-      <c r="Q3" s="335"/>
-      <c r="R3" s="335"/>
-      <c r="S3" s="335"/>
-      <c r="T3" s="335"/>
-      <c r="U3" s="335"/>
-      <c r="V3" s="335"/>
-      <c r="W3" s="336"/>
+      <c r="C3" s="373"/>
+      <c r="D3" s="373"/>
+      <c r="E3" s="373"/>
+      <c r="F3" s="373"/>
+      <c r="G3" s="373"/>
+      <c r="H3" s="373"/>
+      <c r="I3" s="373"/>
+      <c r="J3" s="373"/>
+      <c r="K3" s="373"/>
+      <c r="L3" s="373"/>
+      <c r="M3" s="373"/>
+      <c r="N3" s="373"/>
+      <c r="O3" s="373"/>
+      <c r="P3" s="373"/>
+      <c r="Q3" s="373"/>
+      <c r="R3" s="373"/>
+      <c r="S3" s="373"/>
+      <c r="T3" s="373"/>
+      <c r="U3" s="373"/>
+      <c r="V3" s="373"/>
+      <c r="W3" s="374"/>
     </row>
     <row r="4" spans="2:30" ht="25.5">
       <c r="B4" s="174" t="s">
@@ -18801,37 +18801,37 @@
       </c>
     </row>
     <row r="10" spans="2:30" ht="30">
-      <c r="B10" s="337" t="s">
+      <c r="B10" s="375" t="s">
         <v>1202</v>
       </c>
-      <c r="C10" s="338"/>
-      <c r="D10" s="338"/>
-      <c r="E10" s="338"/>
-      <c r="F10" s="338"/>
-      <c r="G10" s="338"/>
-      <c r="H10" s="338"/>
-      <c r="I10" s="338"/>
-      <c r="J10" s="338"/>
-      <c r="K10" s="338"/>
-      <c r="L10" s="338"/>
-      <c r="M10" s="338"/>
-      <c r="N10" s="338"/>
-      <c r="O10" s="338"/>
-      <c r="P10" s="338"/>
-      <c r="Q10" s="338"/>
-      <c r="R10" s="338"/>
-      <c r="S10" s="338"/>
-      <c r="T10" s="338"/>
-      <c r="U10" s="338"/>
-      <c r="V10" s="338"/>
-      <c r="W10" s="338"/>
-      <c r="X10" s="338"/>
-      <c r="Y10" s="338"/>
-      <c r="Z10" s="338"/>
-      <c r="AA10" s="338"/>
-      <c r="AB10" s="338"/>
-      <c r="AC10" s="338"/>
-      <c r="AD10" s="338"/>
+      <c r="C10" s="376"/>
+      <c r="D10" s="376"/>
+      <c r="E10" s="376"/>
+      <c r="F10" s="376"/>
+      <c r="G10" s="376"/>
+      <c r="H10" s="376"/>
+      <c r="I10" s="376"/>
+      <c r="J10" s="376"/>
+      <c r="K10" s="376"/>
+      <c r="L10" s="376"/>
+      <c r="M10" s="376"/>
+      <c r="N10" s="376"/>
+      <c r="O10" s="376"/>
+      <c r="P10" s="376"/>
+      <c r="Q10" s="376"/>
+      <c r="R10" s="376"/>
+      <c r="S10" s="376"/>
+      <c r="T10" s="376"/>
+      <c r="U10" s="376"/>
+      <c r="V10" s="376"/>
+      <c r="W10" s="376"/>
+      <c r="X10" s="376"/>
+      <c r="Y10" s="376"/>
+      <c r="Z10" s="376"/>
+      <c r="AA10" s="376"/>
+      <c r="AB10" s="376"/>
+      <c r="AC10" s="376"/>
+      <c r="AD10" s="376"/>
     </row>
     <row r="11" spans="2:30" ht="25.5">
       <c r="B11" s="174" t="s">
@@ -19221,30 +19221,30 @@
       </c>
     </row>
     <row r="18" spans="2:30" ht="30">
-      <c r="B18" s="334" t="s">
+      <c r="B18" s="372" t="s">
         <v>1201</v>
       </c>
-      <c r="C18" s="335"/>
-      <c r="D18" s="335"/>
-      <c r="E18" s="335"/>
-      <c r="F18" s="335"/>
-      <c r="G18" s="335"/>
-      <c r="H18" s="335"/>
-      <c r="I18" s="335"/>
-      <c r="J18" s="335"/>
-      <c r="K18" s="335"/>
-      <c r="L18" s="335"/>
-      <c r="M18" s="335"/>
-      <c r="N18" s="335"/>
-      <c r="O18" s="335"/>
-      <c r="P18" s="335"/>
-      <c r="Q18" s="335"/>
-      <c r="R18" s="335"/>
-      <c r="S18" s="335"/>
-      <c r="T18" s="335"/>
-      <c r="U18" s="335"/>
-      <c r="V18" s="335"/>
-      <c r="W18" s="336"/>
+      <c r="C18" s="373"/>
+      <c r="D18" s="373"/>
+      <c r="E18" s="373"/>
+      <c r="F18" s="373"/>
+      <c r="G18" s="373"/>
+      <c r="H18" s="373"/>
+      <c r="I18" s="373"/>
+      <c r="J18" s="373"/>
+      <c r="K18" s="373"/>
+      <c r="L18" s="373"/>
+      <c r="M18" s="373"/>
+      <c r="N18" s="373"/>
+      <c r="O18" s="373"/>
+      <c r="P18" s="373"/>
+      <c r="Q18" s="373"/>
+      <c r="R18" s="373"/>
+      <c r="S18" s="373"/>
+      <c r="T18" s="373"/>
+      <c r="U18" s="373"/>
+      <c r="V18" s="373"/>
+      <c r="W18" s="374"/>
     </row>
     <row r="19" spans="2:30" ht="25.5">
       <c r="B19" s="174" t="s">
@@ -19542,37 +19542,37 @@
       </c>
     </row>
     <row r="25" spans="2:30" ht="30">
-      <c r="B25" s="337" t="s">
+      <c r="B25" s="375" t="s">
         <v>1202</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
-      <c r="G25" s="338"/>
-      <c r="H25" s="338"/>
-      <c r="I25" s="338"/>
-      <c r="J25" s="338"/>
-      <c r="K25" s="338"/>
-      <c r="L25" s="338"/>
-      <c r="M25" s="338"/>
-      <c r="N25" s="338"/>
-      <c r="O25" s="338"/>
-      <c r="P25" s="338"/>
-      <c r="Q25" s="338"/>
-      <c r="R25" s="338"/>
-      <c r="S25" s="338"/>
-      <c r="T25" s="338"/>
-      <c r="U25" s="338"/>
-      <c r="V25" s="338"/>
-      <c r="W25" s="338"/>
-      <c r="X25" s="338"/>
-      <c r="Y25" s="338"/>
-      <c r="Z25" s="338"/>
-      <c r="AA25" s="338"/>
-      <c r="AB25" s="338"/>
-      <c r="AC25" s="338"/>
-      <c r="AD25" s="338"/>
+      <c r="C25" s="376"/>
+      <c r="D25" s="376"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
+      <c r="G25" s="376"/>
+      <c r="H25" s="376"/>
+      <c r="I25" s="376"/>
+      <c r="J25" s="376"/>
+      <c r="K25" s="376"/>
+      <c r="L25" s="376"/>
+      <c r="M25" s="376"/>
+      <c r="N25" s="376"/>
+      <c r="O25" s="376"/>
+      <c r="P25" s="376"/>
+      <c r="Q25" s="376"/>
+      <c r="R25" s="376"/>
+      <c r="S25" s="376"/>
+      <c r="T25" s="376"/>
+      <c r="U25" s="376"/>
+      <c r="V25" s="376"/>
+      <c r="W25" s="376"/>
+      <c r="X25" s="376"/>
+      <c r="Y25" s="376"/>
+      <c r="Z25" s="376"/>
+      <c r="AA25" s="376"/>
+      <c r="AB25" s="376"/>
+      <c r="AC25" s="376"/>
+      <c r="AD25" s="376"/>
     </row>
     <row r="26" spans="2:30" ht="25.5">
       <c r="B26" s="174" t="s">
@@ -32194,66 +32194,66 @@
     </row>
     <row r="2" spans="1:92" s="197" customFormat="1" ht="60" customHeight="1">
       <c r="A2" s="198"/>
-      <c r="B2" s="345" t="s">
+      <c r="B2" s="334" t="s">
         <v>1247</v>
       </c>
-      <c r="C2" s="346"/>
-      <c r="D2" s="347"/>
-      <c r="E2" s="345" t="s">
+      <c r="C2" s="335"/>
+      <c r="D2" s="336"/>
+      <c r="E2" s="334" t="s">
         <v>1248</v>
       </c>
-      <c r="F2" s="346"/>
-      <c r="G2" s="347"/>
-      <c r="H2" s="371" t="s">
+      <c r="F2" s="335"/>
+      <c r="G2" s="336"/>
+      <c r="H2" s="354" t="s">
         <v>1249</v>
       </c>
-      <c r="I2" s="372"/>
-      <c r="J2" s="373"/>
-      <c r="K2" s="371" t="s">
+      <c r="I2" s="355"/>
+      <c r="J2" s="356"/>
+      <c r="K2" s="354" t="s">
         <v>1250</v>
       </c>
-      <c r="L2" s="372"/>
-      <c r="M2" s="373"/>
-      <c r="N2" s="374">
+      <c r="L2" s="355"/>
+      <c r="M2" s="356"/>
+      <c r="N2" s="357">
         <v>0.05</v>
       </c>
-      <c r="O2" s="375"/>
-      <c r="P2" s="376"/>
-      <c r="Q2" s="371" t="s">
+      <c r="O2" s="358"/>
+      <c r="P2" s="359"/>
+      <c r="Q2" s="354" t="s">
         <v>1251</v>
       </c>
-      <c r="R2" s="372"/>
-      <c r="S2" s="373"/>
-      <c r="T2" s="371" t="s">
+      <c r="R2" s="355"/>
+      <c r="S2" s="356"/>
+      <c r="T2" s="354" t="s">
         <v>1252</v>
       </c>
-      <c r="U2" s="372"/>
-      <c r="V2" s="373"/>
-      <c r="W2" s="348" t="s">
+      <c r="U2" s="355"/>
+      <c r="V2" s="356"/>
+      <c r="W2" s="337" t="s">
         <v>1253</v>
       </c>
-      <c r="X2" s="349"/>
-      <c r="Y2" s="350"/>
-      <c r="Z2" s="348" t="s">
+      <c r="X2" s="338"/>
+      <c r="Y2" s="339"/>
+      <c r="Z2" s="337" t="s">
         <v>1254</v>
       </c>
-      <c r="AA2" s="349"/>
-      <c r="AB2" s="350"/>
-      <c r="AC2" s="348" t="s">
+      <c r="AA2" s="338"/>
+      <c r="AB2" s="339"/>
+      <c r="AC2" s="337" t="s">
         <v>1255</v>
       </c>
-      <c r="AD2" s="349"/>
-      <c r="AE2" s="350"/>
-      <c r="AF2" s="351" t="s">
+      <c r="AD2" s="338"/>
+      <c r="AE2" s="339"/>
+      <c r="AF2" s="340" t="s">
         <v>1256</v>
       </c>
-      <c r="AG2" s="352"/>
-      <c r="AH2" s="353"/>
-      <c r="AI2" s="351" t="s">
+      <c r="AG2" s="341"/>
+      <c r="AH2" s="342"/>
+      <c r="AI2" s="340" t="s">
         <v>1257</v>
       </c>
-      <c r="AJ2" s="352"/>
-      <c r="AK2" s="353"/>
+      <c r="AJ2" s="341"/>
+      <c r="AK2" s="342"/>
       <c r="AL2" s="198"/>
       <c r="AM2" s="198"/>
       <c r="AN2" s="198"/>
@@ -32575,71 +32575,71 @@
     <row r="5" spans="1:92" s="197" customFormat="1" ht="60" customHeight="1">
       <c r="A5" s="198"/>
       <c r="B5" s="198"/>
-      <c r="C5" s="345" t="s">
+      <c r="C5" s="334" t="s">
         <v>201</v>
       </c>
-      <c r="D5" s="346"/>
-      <c r="E5" s="347"/>
-      <c r="F5" s="345" t="s">
+      <c r="D5" s="335"/>
+      <c r="E5" s="336"/>
+      <c r="F5" s="334" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="346"/>
-      <c r="H5" s="347"/>
-      <c r="I5" s="345" t="s">
+      <c r="G5" s="335"/>
+      <c r="H5" s="336"/>
+      <c r="I5" s="334" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="346"/>
-      <c r="K5" s="347"/>
-      <c r="L5" s="345" t="s">
+      <c r="J5" s="335"/>
+      <c r="K5" s="336"/>
+      <c r="L5" s="334" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="346"/>
-      <c r="N5" s="347"/>
-      <c r="O5" s="345" t="s">
+      <c r="M5" s="335"/>
+      <c r="N5" s="336"/>
+      <c r="O5" s="334" t="s">
         <v>71</v>
       </c>
-      <c r="P5" s="346"/>
-      <c r="Q5" s="347"/>
-      <c r="R5" s="345" t="s">
+      <c r="P5" s="335"/>
+      <c r="Q5" s="336"/>
+      <c r="R5" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="S5" s="346"/>
-      <c r="T5" s="347"/>
-      <c r="U5" s="348" t="s">
+      <c r="S5" s="335"/>
+      <c r="T5" s="336"/>
+      <c r="U5" s="337" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="349"/>
-      <c r="W5" s="350"/>
-      <c r="X5" s="348" t="s">
+      <c r="V5" s="338"/>
+      <c r="W5" s="339"/>
+      <c r="X5" s="337" t="s">
         <v>94</v>
       </c>
-      <c r="Y5" s="349"/>
-      <c r="Z5" s="350"/>
-      <c r="AA5" s="348" t="s">
+      <c r="Y5" s="338"/>
+      <c r="Z5" s="339"/>
+      <c r="AA5" s="337" t="s">
         <v>86</v>
       </c>
-      <c r="AB5" s="349"/>
-      <c r="AC5" s="350"/>
-      <c r="AD5" s="348" t="s">
+      <c r="AB5" s="338"/>
+      <c r="AC5" s="339"/>
+      <c r="AD5" s="337" t="s">
         <v>67</v>
       </c>
-      <c r="AE5" s="349"/>
-      <c r="AF5" s="350"/>
-      <c r="AG5" s="371" t="s">
+      <c r="AE5" s="338"/>
+      <c r="AF5" s="339"/>
+      <c r="AG5" s="354" t="s">
         <v>1270</v>
       </c>
-      <c r="AH5" s="372"/>
-      <c r="AI5" s="373"/>
-      <c r="AJ5" s="371" t="s">
+      <c r="AH5" s="355"/>
+      <c r="AI5" s="356"/>
+      <c r="AJ5" s="354" t="s">
         <v>1271</v>
       </c>
-      <c r="AK5" s="372"/>
-      <c r="AL5" s="373"/>
-      <c r="AM5" s="351" t="s">
+      <c r="AK5" s="355"/>
+      <c r="AL5" s="356"/>
+      <c r="AM5" s="340" t="s">
         <v>1272</v>
       </c>
-      <c r="AN5" s="352"/>
-      <c r="AO5" s="353"/>
+      <c r="AN5" s="341"/>
+      <c r="AO5" s="342"/>
       <c r="AP5" s="198"/>
       <c r="AQ5" s="198"/>
       <c r="AR5" s="214"/>
@@ -33162,61 +33162,61 @@
       <c r="A8" s="198"/>
       <c r="B8" s="198"/>
       <c r="C8" s="294"/>
-      <c r="D8" s="345" t="s">
+      <c r="D8" s="334" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="347"/>
-      <c r="G8" s="345" t="s">
+      <c r="E8" s="335"/>
+      <c r="F8" s="336"/>
+      <c r="G8" s="334" t="s">
         <v>83</v>
       </c>
-      <c r="H8" s="346"/>
-      <c r="I8" s="347"/>
-      <c r="J8" s="345" t="s">
+      <c r="H8" s="335"/>
+      <c r="I8" s="336"/>
+      <c r="J8" s="334" t="s">
         <v>749</v>
       </c>
-      <c r="K8" s="346"/>
-      <c r="L8" s="347"/>
-      <c r="M8" s="345" t="s">
+      <c r="K8" s="335"/>
+      <c r="L8" s="336"/>
+      <c r="M8" s="334" t="s">
         <v>92</v>
       </c>
-      <c r="N8" s="346"/>
-      <c r="O8" s="347"/>
-      <c r="P8" s="345" t="s">
+      <c r="N8" s="335"/>
+      <c r="O8" s="336"/>
+      <c r="P8" s="334" t="s">
         <v>90</v>
       </c>
-      <c r="Q8" s="346"/>
-      <c r="R8" s="347"/>
-      <c r="S8" s="345" t="s">
+      <c r="Q8" s="335"/>
+      <c r="R8" s="336"/>
+      <c r="S8" s="334" t="s">
         <v>221</v>
       </c>
-      <c r="T8" s="346"/>
-      <c r="U8" s="347"/>
-      <c r="V8" s="348" t="s">
+      <c r="T8" s="335"/>
+      <c r="U8" s="336"/>
+      <c r="V8" s="337" t="s">
         <v>81</v>
       </c>
-      <c r="W8" s="349"/>
-      <c r="X8" s="350"/>
-      <c r="Y8" s="348" t="s">
+      <c r="W8" s="338"/>
+      <c r="X8" s="339"/>
+      <c r="Y8" s="337" t="s">
         <v>74</v>
       </c>
-      <c r="Z8" s="349"/>
-      <c r="AA8" s="350"/>
-      <c r="AB8" s="348" t="s">
+      <c r="Z8" s="338"/>
+      <c r="AA8" s="339"/>
+      <c r="AB8" s="337" t="s">
         <v>102</v>
       </c>
-      <c r="AC8" s="349"/>
-      <c r="AD8" s="350"/>
-      <c r="AE8" s="348" t="s">
+      <c r="AC8" s="338"/>
+      <c r="AD8" s="339"/>
+      <c r="AE8" s="337" t="s">
         <v>1278</v>
       </c>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="371" t="s">
+      <c r="AF8" s="338"/>
+      <c r="AG8" s="339"/>
+      <c r="AH8" s="354" t="s">
         <v>1279</v>
       </c>
-      <c r="AI8" s="372"/>
-      <c r="AJ8" s="373"/>
+      <c r="AI8" s="355"/>
+      <c r="AJ8" s="356"/>
       <c r="AK8" s="198"/>
       <c r="AL8" s="198"/>
       <c r="AM8" s="198"/>
@@ -33700,56 +33700,56 @@
       <c r="B11" s="198"/>
       <c r="C11" s="198"/>
       <c r="D11" s="198"/>
-      <c r="E11" s="345" t="s">
+      <c r="E11" s="334" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="346"/>
-      <c r="G11" s="347"/>
-      <c r="H11" s="345" t="s">
+      <c r="F11" s="335"/>
+      <c r="G11" s="336"/>
+      <c r="H11" s="334" t="s">
         <v>1286</v>
       </c>
-      <c r="I11" s="346"/>
-      <c r="J11" s="347"/>
-      <c r="K11" s="345" t="s">
+      <c r="I11" s="335"/>
+      <c r="J11" s="336"/>
+      <c r="K11" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="346"/>
-      <c r="M11" s="347"/>
-      <c r="N11" s="345" t="s">
+      <c r="L11" s="335"/>
+      <c r="M11" s="336"/>
+      <c r="N11" s="334" t="s">
         <v>93</v>
       </c>
-      <c r="O11" s="346"/>
-      <c r="P11" s="347"/>
-      <c r="Q11" s="345" t="s">
+      <c r="O11" s="335"/>
+      <c r="P11" s="336"/>
+      <c r="Q11" s="334" t="s">
         <v>738</v>
       </c>
-      <c r="R11" s="346"/>
-      <c r="S11" s="347"/>
-      <c r="T11" s="345" t="s">
+      <c r="R11" s="335"/>
+      <c r="S11" s="336"/>
+      <c r="T11" s="334" t="s">
         <v>89</v>
       </c>
-      <c r="U11" s="346"/>
-      <c r="V11" s="347"/>
-      <c r="W11" s="348" t="s">
+      <c r="U11" s="335"/>
+      <c r="V11" s="336"/>
+      <c r="W11" s="337" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="349"/>
-      <c r="Y11" s="350"/>
-      <c r="Z11" s="348" t="s">
+      <c r="X11" s="338"/>
+      <c r="Y11" s="339"/>
+      <c r="Z11" s="337" t="s">
         <v>1287</v>
       </c>
-      <c r="AA11" s="349"/>
-      <c r="AB11" s="350"/>
-      <c r="AC11" s="348" t="s">
+      <c r="AA11" s="338"/>
+      <c r="AB11" s="339"/>
+      <c r="AC11" s="337" t="s">
         <v>1288</v>
       </c>
-      <c r="AD11" s="349"/>
-      <c r="AE11" s="350"/>
-      <c r="AF11" s="351" t="s">
+      <c r="AD11" s="338"/>
+      <c r="AE11" s="339"/>
+      <c r="AF11" s="340" t="s">
         <v>1289</v>
       </c>
-      <c r="AG11" s="352"/>
-      <c r="AH11" s="353"/>
+      <c r="AG11" s="341"/>
+      <c r="AH11" s="342"/>
       <c r="AI11" s="198"/>
       <c r="AJ11" s="198"/>
       <c r="AK11" s="198"/>

--- a/docs/100_鍵盤按鍵與編碼對映.xlsx
+++ b/docs/100_鍵盤按鍵與編碼對映.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40932250-311B-47D1-93E7-3A81F02E023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011F2849-2843-4914-A78E-BA487B39C5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4800" yWindow="360" windowWidth="38640" windowHeight="15720" tabRatio="708" xr2:uid="{B739CF38-08F3-4214-89CB-36FDF4581D42}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" activeTab="1" xr2:uid="{B739CF38-08F3-4214-89CB-36FDF4581D42}"/>
   </bookViews>
   <sheets>
     <sheet name="【拼音類】鍵盤" sheetId="14" r:id="rId1"/>
@@ -397,7 +397,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4074" uniqueCount="1348">
   <si>
     <t>huan_ciat_tps</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -9226,6 +9226,50 @@
     <t>入聲</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>中音調</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>促聲調</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>低音調</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（三）陰去</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ptkh</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> （二）上声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（七）陽去</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（五）陽平</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（一）陰平</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（四）陰入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（八）陽入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -9234,7 +9278,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="General;;"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="170">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -9926,6 +9970,7 @@
     <font>
       <sz val="20"/>
       <name val="宋体"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="24"/>
@@ -9981,6 +10026,7 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="136"/>
     </font>
     <font>
       <b/>
@@ -10000,6 +10046,7 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="136"/>
     </font>
     <font>
       <b/>
@@ -10025,6 +10072,7 @@
     <font>
       <sz val="24"/>
       <name val="宋体"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="26"/>
@@ -10107,6 +10155,7 @@
     <font>
       <sz val="18"/>
       <name val="宋体"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="24"/>
@@ -10361,6 +10410,14 @@
       <color rgb="FFFF0000"/>
       <name val="Noto Serif TC Black"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFC00000"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="25">
@@ -10884,7 +10941,7 @@
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="377">
+  <cellXfs count="381">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11881,6 +11938,15 @@
     <xf numFmtId="9" fontId="162" fillId="19" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="159" fillId="24" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="24" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="24" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="166" fillId="24" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11888,15 +11954,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="167" fillId="24" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="24" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="24" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="24" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="168" fillId="24" borderId="25" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11931,6 +11988,18 @@
     </xf>
     <xf numFmtId="0" fontId="92" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="169" fillId="19" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="169" fillId="19" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="169" fillId="19" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="19" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -14014,11 +14083,11 @@
       <c r="AC3" s="231"/>
       <c r="AD3" s="228"/>
       <c r="AE3" s="232"/>
-      <c r="AF3" s="363" t="s">
+      <c r="AF3" s="360" t="s">
         <v>1326</v>
       </c>
-      <c r="AG3" s="364"/>
-      <c r="AH3" s="365"/>
+      <c r="AG3" s="361"/>
+      <c r="AH3" s="362"/>
       <c r="AI3" s="233"/>
       <c r="AJ3" s="234"/>
       <c r="AK3" s="235"/>
@@ -14067,11 +14136,11 @@
       <c r="AC4" s="253"/>
       <c r="AD4" s="251"/>
       <c r="AE4" s="252"/>
-      <c r="AF4" s="360" t="s">
+      <c r="AF4" s="363" t="s">
         <v>1334</v>
       </c>
-      <c r="AG4" s="361"/>
-      <c r="AH4" s="362" t="s">
+      <c r="AG4" s="364"/>
+      <c r="AH4" s="365" t="s">
         <v>1268</v>
       </c>
       <c r="AI4" s="257"/>
@@ -14192,21 +14261,21 @@
       <c r="AD6" s="231"/>
       <c r="AE6" s="228"/>
       <c r="AF6" s="232"/>
-      <c r="AG6" s="363" t="s">
+      <c r="AG6" s="360" t="s">
         <v>1327</v>
       </c>
-      <c r="AH6" s="364"/>
-      <c r="AI6" s="365"/>
-      <c r="AJ6" s="363" t="s">
+      <c r="AH6" s="361"/>
+      <c r="AI6" s="362"/>
+      <c r="AJ6" s="360" t="s">
         <v>1328</v>
       </c>
-      <c r="AK6" s="364"/>
-      <c r="AL6" s="365"/>
-      <c r="AM6" s="363" t="s">
+      <c r="AK6" s="361"/>
+      <c r="AL6" s="362"/>
+      <c r="AM6" s="360" t="s">
         <v>1330</v>
       </c>
-      <c r="AN6" s="364"/>
-      <c r="AO6" s="365"/>
+      <c r="AN6" s="361"/>
+      <c r="AO6" s="362"/>
       <c r="AP6" s="198"/>
       <c r="AQ6" s="198"/>
       <c r="AR6" s="214"/>
@@ -14245,21 +14314,21 @@
       <c r="AD7" s="253"/>
       <c r="AE7" s="254"/>
       <c r="AF7" s="292"/>
-      <c r="AG7" s="360" t="s">
+      <c r="AG7" s="363" t="s">
         <v>1275</v>
       </c>
-      <c r="AH7" s="361"/>
-      <c r="AI7" s="362"/>
-      <c r="AJ7" s="360" t="s">
+      <c r="AH7" s="364"/>
+      <c r="AI7" s="365"/>
+      <c r="AJ7" s="363" t="s">
         <v>1277</v>
       </c>
-      <c r="AK7" s="361"/>
-      <c r="AL7" s="362"/>
-      <c r="AM7" s="360" t="s">
+      <c r="AK7" s="364"/>
+      <c r="AL7" s="365"/>
+      <c r="AM7" s="363" t="s">
         <v>1335</v>
       </c>
-      <c r="AN7" s="361"/>
-      <c r="AO7" s="362"/>
+      <c r="AN7" s="364"/>
+      <c r="AO7" s="365"/>
       <c r="AP7" s="240"/>
       <c r="AQ7" s="240"/>
       <c r="AR7" s="187"/>
@@ -14365,11 +14434,11 @@
       <c r="AB9" s="227"/>
       <c r="AC9" s="228"/>
       <c r="AD9" s="229"/>
-      <c r="AE9" s="363" t="s">
+      <c r="AE9" s="360" t="s">
         <v>1325</v>
       </c>
-      <c r="AF9" s="364"/>
-      <c r="AG9" s="365"/>
+      <c r="AF9" s="361"/>
+      <c r="AG9" s="362"/>
       <c r="AH9" s="227"/>
       <c r="AI9" s="228"/>
       <c r="AJ9" s="229"/>
@@ -14414,11 +14483,11 @@
       <c r="AB10" s="253"/>
       <c r="AC10" s="251"/>
       <c r="AD10" s="255"/>
-      <c r="AE10" s="360" t="s">
+      <c r="AE10" s="363" t="s">
         <v>1324</v>
       </c>
-      <c r="AF10" s="361"/>
-      <c r="AG10" s="362"/>
+      <c r="AF10" s="364"/>
+      <c r="AG10" s="365"/>
       <c r="AH10" s="253"/>
       <c r="AI10" s="251"/>
       <c r="AJ10" s="255"/>
@@ -14528,14 +14597,14 @@
       <c r="Z12" s="227"/>
       <c r="AA12" s="230"/>
       <c r="AB12" s="229"/>
-      <c r="AC12" s="363"/>
-      <c r="AD12" s="364"/>
-      <c r="AE12" s="365"/>
-      <c r="AF12" s="363" t="s">
+      <c r="AC12" s="360"/>
+      <c r="AD12" s="361"/>
+      <c r="AE12" s="362"/>
+      <c r="AF12" s="360" t="s">
         <v>1329</v>
       </c>
-      <c r="AG12" s="364"/>
-      <c r="AH12" s="365"/>
+      <c r="AG12" s="361"/>
+      <c r="AH12" s="362"/>
       <c r="AI12" s="198"/>
       <c r="AJ12" s="198"/>
       <c r="AK12" s="198"/>
@@ -14579,14 +14648,14 @@
       <c r="Z13" s="253"/>
       <c r="AA13" s="251"/>
       <c r="AB13" s="255"/>
-      <c r="AC13" s="360"/>
-      <c r="AD13" s="361"/>
-      <c r="AE13" s="362"/>
-      <c r="AF13" s="360" t="s">
+      <c r="AC13" s="363"/>
+      <c r="AD13" s="364"/>
+      <c r="AE13" s="365"/>
+      <c r="AF13" s="363" t="s">
         <v>1324</v>
       </c>
-      <c r="AG13" s="361"/>
-      <c r="AH13" s="362"/>
+      <c r="AG13" s="364"/>
+      <c r="AH13" s="365"/>
       <c r="AI13" s="240"/>
       <c r="AJ13" s="240"/>
       <c r="AK13" s="240"/>
@@ -18443,12 +18512,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="AE9:AG9"/>
-    <mergeCell ref="AE10:AG10"/>
-    <mergeCell ref="AC13:AE13"/>
-    <mergeCell ref="AF13:AH13"/>
-    <mergeCell ref="AM6:AO6"/>
-    <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="T4:V4"/>
     <mergeCell ref="AF3:AH3"/>
@@ -18456,8 +18519,14 @@
     <mergeCell ref="AC12:AE12"/>
     <mergeCell ref="AF12:AH12"/>
     <mergeCell ref="AG6:AI6"/>
+    <mergeCell ref="AG7:AI7"/>
+    <mergeCell ref="AE9:AG9"/>
+    <mergeCell ref="AE10:AG10"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="AF13:AH13"/>
+    <mergeCell ref="AM6:AO6"/>
+    <mergeCell ref="AM7:AO7"/>
     <mergeCell ref="AJ6:AL6"/>
-    <mergeCell ref="AG7:AI7"/>
     <mergeCell ref="AJ7:AL7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -32318,21 +32387,31 @@
       <c r="E3" s="219"/>
       <c r="F3" s="217"/>
       <c r="G3" s="220"/>
-      <c r="H3" s="221"/>
-      <c r="I3" s="222"/>
-      <c r="J3" s="223"/>
-      <c r="K3" s="221"/>
-      <c r="L3" s="222"/>
-      <c r="M3" s="223"/>
-      <c r="N3" s="224"/>
-      <c r="O3" s="225"/>
-      <c r="P3" s="226"/>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="222"/>
-      <c r="S3" s="223"/>
-      <c r="T3" s="221"/>
-      <c r="U3" s="222"/>
-      <c r="V3" s="223"/>
+      <c r="H3" s="377" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I3" s="378"/>
+      <c r="J3" s="379"/>
+      <c r="K3" s="377" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L3" s="378"/>
+      <c r="M3" s="379"/>
+      <c r="N3" s="377" t="s">
+        <v>1337</v>
+      </c>
+      <c r="O3" s="378"/>
+      <c r="P3" s="379"/>
+      <c r="Q3" s="377" t="s">
+        <v>1329</v>
+      </c>
+      <c r="R3" s="378"/>
+      <c r="S3" s="379"/>
+      <c r="T3" s="377" t="s">
+        <v>1338</v>
+      </c>
+      <c r="U3" s="378"/>
+      <c r="V3" s="379"/>
       <c r="W3" s="227" t="s">
         <v>171</v>
       </c>
@@ -32400,36 +32479,36 @@
         <v>725</v>
       </c>
       <c r="I4" s="246"/>
-      <c r="J4" s="247" t="s">
-        <v>611</v>
+      <c r="J4" s="380" t="s">
+        <v>1340</v>
       </c>
       <c r="K4" s="248" t="s">
         <v>723</v>
       </c>
-      <c r="L4" s="249"/>
-      <c r="M4" s="247" t="s">
-        <v>1264</v>
+      <c r="L4" s="246"/>
+      <c r="M4" s="380" t="s">
+        <v>1342</v>
       </c>
       <c r="N4" s="245" t="s">
         <v>724</v>
       </c>
       <c r="O4" s="246"/>
-      <c r="P4" s="247" t="s">
-        <v>605</v>
+      <c r="P4" s="380" t="s">
+        <v>1343</v>
       </c>
       <c r="Q4" s="248" t="s">
         <v>722</v>
       </c>
-      <c r="R4" s="249"/>
-      <c r="S4" s="247" t="s">
-        <v>624</v>
+      <c r="R4" s="246"/>
+      <c r="S4" s="380" t="s">
+        <v>1344</v>
       </c>
       <c r="T4" s="248" t="s">
         <v>1336</v>
       </c>
       <c r="U4" s="246"/>
       <c r="V4" s="247" t="s">
-        <v>1265</v>
+        <v>1341</v>
       </c>
       <c r="W4" s="250" t="s">
         <v>1266</v>
@@ -32827,12 +32906,16 @@
       <c r="AD6" s="231"/>
       <c r="AE6" s="228"/>
       <c r="AF6" s="232"/>
-      <c r="AG6" s="221"/>
-      <c r="AH6" s="222"/>
-      <c r="AI6" s="223"/>
-      <c r="AJ6" s="221"/>
-      <c r="AK6" s="222"/>
-      <c r="AL6" s="223"/>
+      <c r="AG6" s="377" t="s">
+        <v>1327</v>
+      </c>
+      <c r="AH6" s="378"/>
+      <c r="AI6" s="379"/>
+      <c r="AJ6" s="377" t="s">
+        <v>1328</v>
+      </c>
+      <c r="AK6" s="378"/>
+      <c r="AL6" s="379"/>
       <c r="AM6" s="227"/>
       <c r="AN6" s="285"/>
       <c r="AO6" s="287"/>
@@ -33034,16 +33117,16 @@
         <v>45</v>
       </c>
       <c r="AG7" s="248"/>
-      <c r="AH7" s="249"/>
-      <c r="AI7" s="293" t="s">
-        <v>1275</v>
+      <c r="AH7" s="246"/>
+      <c r="AI7" s="380" t="s">
+        <v>1346</v>
       </c>
       <c r="AJ7" s="248" t="s">
         <v>1276</v>
       </c>
-      <c r="AK7" s="249"/>
-      <c r="AL7" s="293" t="s">
-        <v>1277</v>
+      <c r="AK7" s="246"/>
+      <c r="AL7" s="380" t="s">
+        <v>1347</v>
       </c>
       <c r="AM7" s="253"/>
       <c r="AN7" s="254"/>
@@ -33381,9 +33464,11 @@
       <c r="AE9" s="227"/>
       <c r="AF9" s="228"/>
       <c r="AG9" s="229"/>
-      <c r="AH9" s="221"/>
-      <c r="AI9" s="222"/>
-      <c r="AJ9" s="223"/>
+      <c r="AH9" s="377" t="s">
+        <v>1325</v>
+      </c>
+      <c r="AI9" s="378"/>
+      <c r="AJ9" s="379"/>
       <c r="AK9" s="198"/>
       <c r="AL9" s="198"/>
       <c r="AM9" s="198"/>
@@ -33576,9 +33661,9 @@
         <v>215</v>
       </c>
       <c r="AH10" s="248"/>
-      <c r="AI10" s="249"/>
-      <c r="AJ10" s="293" t="s">
-        <v>1285</v>
+      <c r="AI10" s="246"/>
+      <c r="AJ10" s="380" t="s">
+        <v>1345</v>
       </c>
       <c r="AK10" s="240"/>
       <c r="AL10" s="240"/>
@@ -41959,6 +42044,16 @@
       <c r="AS153" s="187"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="AJ6:AL6"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="AG6:AI6"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
